--- a/branches/migration/2026.0.1-template-v0.11.0/StructureDefinition-mii-pr-studie-beteiligte-person.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.0/StructureDefinition-mii-pr-studie-beteiligte-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T21:13:29+00:00</t>
+    <t>2026-08-19T21:26:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.0/StructureDefinition-mii-pr-studie-beteiligte-person.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.0/StructureDefinition-mii-pr-studie-beteiligte-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T21:26:17+00:00</t>
+    <t>2026-08-20T09:40:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.0/StructureDefinition-mii-pr-studie-beteiligte-person.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.0/StructureDefinition-mii-pr-studie-beteiligte-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T09:40:04+00:00</t>
+    <t>2026-08-20T09:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.0/StructureDefinition-mii-pr-studie-beteiligte-person.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.0/StructureDefinition-mii-pr-studie-beteiligte-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T09:46:33+00:00</t>
+    <t>2026-08-20T09:52:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.0/StructureDefinition-mii-pr-studie-beteiligte-person.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.0/StructureDefinition-mii-pr-studie-beteiligte-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T09:52:29+00:00</t>
+    <t>2026-08-20T10:04:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
